--- a/analyzation/translucency_summary_merged.xlsx
+++ b/analyzation/translucency_summary_merged.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSprojects\TaihuStone\analyzation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0601CA72-38AB-4CEA-9D18-3327397A1649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="7720" windowWidth="14850" windowHeight="10310"/>
+    <workbookView windowWidth="25400" windowHeight="17080"/>
   </bookViews>
   <sheets>
     <sheet name="translucency_summary_merged" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
   <si>
     <t>FileName</t>
   </si>
@@ -87,13 +89,79 @@
     <t>FinalEdgesTotal</t>
   </si>
   <si>
-    <t>Used_edges_detail_(edge_index,_from,_to,_usage_count)</t>
-  </si>
-  <si>
-    <t>namaqualand_translucency_summary25252525.txt</t>
-  </si>
-  <si>
-    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_translucency_summary25252525.txt</t>
+    <t>Porosity</t>
+  </si>
+  <si>
+    <t>Floating_voxel_count_(removed_from_SDF)</t>
+  </si>
+  <si>
+    <t>Unsupported_voxel_count</t>
+  </si>
+  <si>
+    <t>namaqualand_0001.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_0001.txt</t>
+  </si>
+  <si>
+    <t>7   num: 4</t>
+  </si>
+  <si>
+    <t>0.000000, 0.000000, 0.000000, 1.000000</t>
+  </si>
+  <si>
+    <t>namaqualand_0010.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_0010.txt</t>
+  </si>
+  <si>
+    <t>6   num: 9</t>
+  </si>
+  <si>
+    <t>0.000000, 0.000000, 1.000000, 0.000000</t>
+  </si>
+  <si>
+    <t>namaqualand_0100.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_0100.txt</t>
+  </si>
+  <si>
+    <t>6   num: 6</t>
+  </si>
+  <si>
+    <t>0.000000, 1.000000, 0.000000, 0.000000</t>
+  </si>
+  <si>
+    <t>namaqualand_0202060.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_0202060.txt</t>
+  </si>
+  <si>
+    <t>9   num: 2</t>
+  </si>
+  <si>
+    <t>0.000000, 0.200000, 0.200000, 0.600000</t>
+  </si>
+  <si>
+    <t>namaqualand_1000.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_1000.txt</t>
+  </si>
+  <si>
+    <t>7   num: 5</t>
+  </si>
+  <si>
+    <t>1.000000, 0.000000, 0.000000, 0.000000</t>
+  </si>
+  <si>
+    <t>namaqualand_25252525.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_25252525.txt</t>
   </si>
   <si>
     <t>8   num: 3</t>
@@ -102,28 +170,109 @@
     <t>0.250000, 0.250000, 0.250000, 0.250000</t>
   </si>
   <si>
-    <t>namaqualand_translucency_summary50101030.txt</t>
-  </si>
-  <si>
-    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_translucency_summary50101030.txt</t>
+    <t>namaqualand_50101030adj15.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_50101030adj15.txt</t>
+  </si>
+  <si>
+    <t>6   num: 2</t>
+  </si>
+  <si>
+    <t>0.500000, 0.100000, 0.100000, 0.300000</t>
+  </si>
+  <si>
+    <t>namaqualand_50101030adj25.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_50101030adj25.txt</t>
+  </si>
+  <si>
+    <t>7   num: 7</t>
+  </si>
+  <si>
+    <t>namaqualand_50101030adj35.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_50101030adj35.txt</t>
   </si>
   <si>
     <t>7   num: 9</t>
   </si>
   <si>
-    <t>0.500000, 0.100000, 0.100000, 0.300000</t>
+    <t>namaqualand_50101030adj45.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_50101030adj45.txt</t>
+  </si>
+  <si>
+    <t>7   num: 10</t>
+  </si>
+  <si>
+    <t>namaqualand_50101030adj55.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_50101030adj55.txt</t>
+  </si>
+  <si>
+    <t>8   num: 7</t>
+  </si>
+  <si>
+    <t>namaqualand_5501134.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_5501134.txt</t>
+  </si>
+  <si>
+    <t>7   num: 8</t>
+  </si>
+  <si>
+    <t>0.550000, 0.000000, 0.110000, 0.340000</t>
+  </si>
+  <si>
+    <t>namaqualand_5511034.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_5511034.txt</t>
+  </si>
+  <si>
+    <t>7   num: 6</t>
+  </si>
+  <si>
+    <t>0.550000, 0.110000, 0.000000, 0.340000</t>
+  </si>
+  <si>
+    <t>namaqualand_7015150.txt</t>
+  </si>
+  <si>
+    <t>D:\VSprojects\TaihuStone\analyzation\txt\namaqualand_7015150.txt</t>
+  </si>
+  <si>
+    <t>0.700000, 0.150000, 0.150000, 0.000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -131,24 +280,45 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -157,7 +327,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -166,31 +335,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,7 +342,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -207,7 +350,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -216,15 +358,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -233,24 +366,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -259,7 +381,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -267,14 +409,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -288,175 +422,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,6 +613,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -491,7 +653,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -526,15 +688,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -550,17 +703,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -576,191 +723,221 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -809,7 +986,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -842,26 +1019,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -894,23 +1054,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1052,21 +1195,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="16" max="16" width="6.83333333333333" customWidth="1"/>
+    <col min="17" max="17" width="4.33333333333333" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1130,133 +1273,1014 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>0.76475499999999996</v>
+        <v>0.962482</v>
       </c>
       <c r="E2">
-        <v>0.89891399999999999</v>
+        <v>0.380712</v>
       </c>
       <c r="F2">
-        <v>0.34385599999999999</v>
+        <v>0.350102</v>
       </c>
       <c r="G2">
-        <v>0.99031000000000002</v>
+        <v>0.459827</v>
       </c>
       <c r="H2">
-        <v>0.82594000000000001</v>
+        <v>0.962482</v>
       </c>
       <c r="I2">
-        <v>0.76475499999999996</v>
+        <v>0.962482</v>
       </c>
       <c r="J2">
         <v>60</v>
       </c>
       <c r="K2">
-        <v>2.1166670000000001</v>
+        <v>2.333333</v>
       </c>
       <c r="L2">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>54</v>
+      </c>
+      <c r="N2">
+        <v>0.516667</v>
+      </c>
+      <c r="O2">
+        <v>0.9</v>
+      </c>
+      <c r="P2">
+        <v>0.627788</v>
+      </c>
+      <c r="Q2">
+        <v>60</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2">
+        <v>70</v>
+      </c>
+      <c r="T2">
+        <v>124</v>
+      </c>
+      <c r="U2">
+        <v>0.646198</v>
+      </c>
+      <c r="V2">
+        <v>27</v>
+      </c>
+      <c r="W2">
+        <v>10447</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>0.999665</v>
+      </c>
+      <c r="E3">
+        <v>0.570868</v>
+      </c>
+      <c r="F3">
+        <v>0.380865</v>
+      </c>
+      <c r="G3">
+        <v>0.999665</v>
+      </c>
+      <c r="H3">
+        <v>0.249465</v>
+      </c>
+      <c r="I3">
+        <v>0.999665</v>
+      </c>
+      <c r="J3">
+        <v>60</v>
+      </c>
+      <c r="K3">
+        <v>2.433333</v>
+      </c>
+      <c r="L3">
+        <v>86</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1.433333</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0.637852</v>
+      </c>
+      <c r="Q3">
+        <v>60</v>
+      </c>
+      <c r="R3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3">
+        <v>54</v>
+      </c>
+      <c r="T3">
+        <v>80</v>
+      </c>
+      <c r="U3">
+        <v>0.487707</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>0.965983</v>
+      </c>
+      <c r="E4">
+        <v>0.005729</v>
+      </c>
+      <c r="F4">
+        <v>0.965983</v>
+      </c>
+      <c r="G4">
+        <v>0.709141</v>
+      </c>
+      <c r="H4">
+        <v>0.077451</v>
+      </c>
+      <c r="I4">
+        <v>0.965983</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+      <c r="K4">
+        <v>17.066667</v>
+      </c>
+      <c r="L4">
+        <v>478</v>
+      </c>
+      <c r="M4">
+        <v>486</v>
+      </c>
+      <c r="N4">
+        <v>7.966667</v>
+      </c>
+      <c r="O4">
+        <v>8.1</v>
+      </c>
+      <c r="P4">
+        <v>0.094196</v>
+      </c>
+      <c r="Q4">
+        <v>60</v>
+      </c>
+      <c r="R4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4">
+        <v>92</v>
+      </c>
+      <c r="T4">
+        <v>103</v>
+      </c>
+      <c r="U4">
+        <v>0.52894</v>
+      </c>
+      <c r="V4">
+        <v>39</v>
+      </c>
+      <c r="W4">
+        <v>6490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>0.856269</v>
+      </c>
+      <c r="E5">
+        <v>0.070883</v>
+      </c>
+      <c r="F5">
+        <v>0.645834</v>
+      </c>
+      <c r="G5">
+        <v>0.964655</v>
+      </c>
+      <c r="H5">
+        <v>0.890285</v>
+      </c>
+      <c r="I5">
+        <v>0.856269</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+      <c r="K5">
+        <v>5.35</v>
+      </c>
+      <c r="L5">
+        <v>139</v>
+      </c>
+      <c r="M5">
+        <v>122</v>
+      </c>
+      <c r="N5">
+        <v>2.316667</v>
+      </c>
+      <c r="O5">
+        <v>2.033333</v>
+      </c>
+      <c r="P5">
+        <v>0.235454</v>
+      </c>
+      <c r="Q5">
+        <v>60</v>
+      </c>
+      <c r="R5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5">
+        <v>97</v>
+      </c>
+      <c r="T5">
+        <v>152</v>
+      </c>
+      <c r="U5">
+        <v>0.694113</v>
+      </c>
+      <c r="V5">
+        <v>335</v>
+      </c>
+      <c r="W5">
+        <v>13582</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <v>0.973146</v>
+      </c>
+      <c r="E6">
+        <v>0.973146</v>
+      </c>
+      <c r="F6">
+        <v>0.32968</v>
+      </c>
+      <c r="G6">
+        <v>0.905118</v>
+      </c>
+      <c r="H6">
+        <v>0.468675</v>
+      </c>
+      <c r="I6">
+        <v>0.973146</v>
+      </c>
+      <c r="J6">
+        <v>60</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>54</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>0.9</v>
+      </c>
+      <c r="O6">
+        <v>0.1</v>
+      </c>
+      <c r="P6">
+        <v>0.995443</v>
+      </c>
+      <c r="Q6">
+        <v>60</v>
+      </c>
+      <c r="R6" t="s">
+        <v>42</v>
+      </c>
+      <c r="S6">
+        <v>61</v>
+      </c>
+      <c r="T6">
+        <v>111</v>
+      </c>
+      <c r="U6">
+        <v>0.586181</v>
+      </c>
+      <c r="V6">
+        <v>6</v>
+      </c>
+      <c r="W6">
+        <v>4954</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>0.764755</v>
+      </c>
+      <c r="E7">
+        <v>0.898914</v>
+      </c>
+      <c r="F7">
+        <v>0.343856</v>
+      </c>
+      <c r="G7">
+        <v>0.99031</v>
+      </c>
+      <c r="H7">
+        <v>0.82594</v>
+      </c>
+      <c r="I7">
+        <v>0.764755</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>2.116667</v>
+      </c>
+      <c r="L7">
         <v>63</v>
       </c>
-      <c r="M2">
+      <c r="M7">
         <v>4</v>
       </c>
-      <c r="N2">
+      <c r="N7">
         <v>1.05</v>
       </c>
-      <c r="O2">
-        <v>6.6667000000000004E-2</v>
-      </c>
-      <c r="P2">
-        <v>0.94195499999999999</v>
-      </c>
-      <c r="Q2">
-        <v>60</v>
-      </c>
-      <c r="R2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2">
+      <c r="O7">
+        <v>0.066667</v>
+      </c>
+      <c r="P7">
+        <v>0.941955</v>
+      </c>
+      <c r="Q7">
+        <v>60</v>
+      </c>
+      <c r="R7" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7">
         <v>62</v>
       </c>
-      <c r="T2">
+      <c r="T7">
         <v>126</v>
       </c>
+      <c r="U7">
+        <v>0.625297</v>
+      </c>
+      <c r="V7">
+        <v>47</v>
+      </c>
+      <c r="W7">
+        <v>11370</v>
+      </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3">
-        <v>0.82636699999999996</v>
-      </c>
-      <c r="E3">
-        <v>0.92371599999999998</v>
-      </c>
-      <c r="F3">
-        <v>0.33336300000000002</v>
-      </c>
-      <c r="G3">
-        <v>0.92767299999999997</v>
-      </c>
-      <c r="H3">
+    <row r="8" spans="1:24">
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.704839</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.825819</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.384386</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.778805</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.585368</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.704839</v>
+      </c>
+      <c r="J8" s="2">
+        <v>60</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2.466667</v>
+      </c>
+      <c r="L8" s="2">
+        <v>71</v>
+      </c>
+      <c r="M8" s="2">
+        <v>17</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1.183333</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.283333</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.910081</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>60</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" s="2">
+        <v>62</v>
+      </c>
+      <c r="T8" s="2">
+        <v>76</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.445107</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>2825</v>
+      </c>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.80842</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.907835</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.347458</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.843882</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.78456</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.80842</v>
+      </c>
+      <c r="J9" s="2">
+        <v>60</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>60</v>
+      </c>
+      <c r="M9" s="2">
+        <v>9</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.965355</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>60</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9" s="2">
+        <v>67</v>
+      </c>
+      <c r="T9" s="2">
+        <v>112</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.560506</v>
+      </c>
+      <c r="V9" s="2">
+        <v>3</v>
+      </c>
+      <c r="W9" s="2">
+        <v>7031</v>
+      </c>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.826367</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.923716</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.333363</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.927673</v>
+      </c>
+      <c r="H10" s="2">
         <v>0.794686</v>
       </c>
-      <c r="I3">
-        <v>0.82636699999999996</v>
-      </c>
-      <c r="J3">
-        <v>60</v>
-      </c>
-      <c r="K3">
-        <v>2.0333329999999998</v>
-      </c>
-      <c r="L3">
+      <c r="I10" s="2">
+        <v>0.826367</v>
+      </c>
+      <c r="J10" s="2">
+        <v>60</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2.033333</v>
+      </c>
+      <c r="L10" s="2">
         <v>57</v>
       </c>
-      <c r="M3">
+      <c r="M10" s="2">
         <v>5</v>
       </c>
-      <c r="N3">
+      <c r="N10" s="2">
         <v>0.95</v>
       </c>
-      <c r="O3">
-        <v>8.3333000000000004E-2</v>
-      </c>
-      <c r="P3">
-        <v>0.96648000000000001</v>
-      </c>
-      <c r="Q3">
-        <v>60</v>
-      </c>
-      <c r="R3" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3">
+      <c r="O10" s="2">
+        <v>0.083333</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.96648</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>60</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" s="2">
         <v>70</v>
       </c>
-      <c r="T3">
+      <c r="T10" s="2">
         <v>120</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.605743</v>
+      </c>
+      <c r="V10" s="2">
+        <v>35</v>
+      </c>
+      <c r="W10" s="2">
+        <v>9419</v>
+      </c>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.82733</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.928655</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.32968</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.928042</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.790767</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.82733</v>
+      </c>
+      <c r="J11" s="2">
+        <v>60</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>56</v>
+      </c>
+      <c r="M11" s="2">
+        <v>4</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.933333</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.066667</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.973152</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>60</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S11" s="2">
+        <v>70</v>
+      </c>
+      <c r="T11" s="2">
+        <v>123</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0.617985</v>
+      </c>
+      <c r="V11" s="2">
+        <v>35</v>
+      </c>
+      <c r="W11" s="2">
+        <v>10350</v>
+      </c>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.834106</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.932588</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.32968</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.936369</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.804024</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.834106</v>
+      </c>
+      <c r="J12" s="2">
+        <v>60</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2</v>
+      </c>
+      <c r="L12" s="2">
+        <v>57</v>
+      </c>
+      <c r="M12" s="2">
+        <v>3</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.975775</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>60</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S12" s="2">
+        <v>70</v>
+      </c>
+      <c r="T12" s="2">
+        <v>132</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.639402</v>
+      </c>
+      <c r="V12" s="2">
+        <v>3</v>
+      </c>
+      <c r="W12" s="2">
+        <v>10682</v>
+      </c>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13">
+        <v>0.880261</v>
+      </c>
+      <c r="E13">
+        <v>0.925509</v>
+      </c>
+      <c r="F13">
+        <v>0.32968</v>
+      </c>
+      <c r="G13">
+        <v>0.927453</v>
+      </c>
+      <c r="H13">
+        <v>0.791798</v>
+      </c>
+      <c r="I13">
+        <v>0.880261</v>
+      </c>
+      <c r="J13">
+        <v>60</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>56</v>
+      </c>
+      <c r="M13">
+        <v>4</v>
+      </c>
+      <c r="N13">
+        <v>0.933333</v>
+      </c>
+      <c r="O13">
+        <v>0.066667</v>
+      </c>
+      <c r="P13">
+        <v>0.971184</v>
+      </c>
+      <c r="Q13">
+        <v>60</v>
+      </c>
+      <c r="R13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13">
+        <v>67</v>
+      </c>
+      <c r="T13">
+        <v>116</v>
+      </c>
+      <c r="U13">
+        <v>0.596016</v>
+      </c>
+      <c r="V13">
+        <v>43</v>
+      </c>
+      <c r="W13">
+        <v>9405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14">
+        <v>0.829299</v>
+      </c>
+      <c r="E14">
+        <v>0.93393</v>
+      </c>
+      <c r="F14">
+        <v>0.32968</v>
+      </c>
+      <c r="G14">
+        <v>0.704958</v>
+      </c>
+      <c r="H14">
+        <v>0.821685</v>
+      </c>
+      <c r="I14">
+        <v>0.829299</v>
+      </c>
+      <c r="J14">
+        <v>60</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>42</v>
+      </c>
+      <c r="M14">
+        <v>18</v>
+      </c>
+      <c r="N14">
+        <v>0.7</v>
+      </c>
+      <c r="O14">
+        <v>0.3</v>
+      </c>
+      <c r="P14">
+        <v>0.976518</v>
+      </c>
+      <c r="Q14">
+        <v>60</v>
+      </c>
+      <c r="R14" t="s">
+        <v>70</v>
+      </c>
+      <c r="S14">
+        <v>65</v>
+      </c>
+      <c r="T14">
+        <v>120</v>
+      </c>
+      <c r="U14">
+        <v>0.596568</v>
+      </c>
+      <c r="V14">
+        <v>11</v>
+      </c>
+      <c r="W14">
+        <v>9086</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15">
+        <v>0.874724</v>
+      </c>
+      <c r="E15">
+        <v>0.965313</v>
+      </c>
+      <c r="F15">
+        <v>0.32968</v>
+      </c>
+      <c r="G15">
+        <v>0.997017</v>
+      </c>
+      <c r="H15">
+        <v>0.430543</v>
+      </c>
+      <c r="I15">
+        <v>0.874724</v>
+      </c>
+      <c r="J15">
+        <v>60</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>60</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0.992028</v>
+      </c>
+      <c r="Q15">
+        <v>60</v>
+      </c>
+      <c r="R15" t="s">
+        <v>73</v>
+      </c>
+      <c r="S15">
+        <v>59</v>
+      </c>
+      <c r="T15">
+        <v>107</v>
+      </c>
+      <c r="U15">
+        <v>0.568572</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>6093</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>